--- a/database/seeders/files/admin-Superadmin.xlsx
+++ b/database/seeders/files/admin-Superadmin.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\Project_sekolah\BE-Absensi-Siswa\database\seeders\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Development\GO\BE-Siswa\database\seeders\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212D3A96-AC6A-4160-97B9-641750DBF816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78030BFD-6AD8-4B84-8D09-F7453B453E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
   <si>
     <t>NISN</t>
   </si>
@@ -43,88 +43,10 @@
     <t>Parent Phone</t>
   </si>
   <si>
-    <t>SuperAdmin1</t>
-  </si>
-  <si>
-    <t>AdminSuper1</t>
-  </si>
-  <si>
-    <t>admin123</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>superadmin</t>
-  </si>
-  <si>
-    <t>0895345570902</t>
-  </si>
-  <si>
-    <t>SuperAdmin2</t>
-  </si>
-  <si>
-    <t>AdminSuper2</t>
-  </si>
-  <si>
-    <t>admin321</t>
-  </si>
-  <si>
-    <t>08380483084</t>
-  </si>
-  <si>
-    <t>Admin</t>
-  </si>
-  <si>
     <t>admin</t>
   </si>
   <si>
-    <t>admin456</t>
-  </si>
-  <si>
-    <t>038048304</t>
-  </si>
-  <si>
-    <t>Alvin</t>
-  </si>
-  <si>
-    <t>alvin</t>
-  </si>
-  <si>
-    <t>alvin123</t>
-  </si>
-  <si>
-    <t>XI-RPL-2</t>
-  </si>
-  <si>
-    <t>siswa</t>
-  </si>
-  <si>
-    <t>081398036877</t>
-  </si>
-  <si>
-    <t>Reihan</t>
-  </si>
-  <si>
-    <t>reihan123</t>
-  </si>
-  <si>
-    <t>Ozan</t>
-  </si>
-  <si>
-    <t>ozan123</t>
-  </si>
-  <si>
-    <t>0895809478855</t>
-  </si>
-  <si>
-    <t>Fitri</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>08999119099</t>
+    <t>1082023</t>
   </si>
 </sst>
 </file>
@@ -424,164 +346,80 @@
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>11111111</v>
+        <v>12345678</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>22222222</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>12345678</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>87654321</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>123454321</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>567898765</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>231231331</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
